--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43149-2026 artfynd.xlsx
+++ b/artfynd/A 43149-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153505</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153506</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
